--- a/erp-server/erp-server-file/src/main/resources/excel/sys/templateManagementExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/sys/templateManagementExport.xlsx
@@ -58,7 +58,7 @@
     <t>{.name}</t>
   </si>
   <si>
-    <t>{.typeName}</t>
+    <t>{.bizTypeName}</t>
   </si>
   <si>
     <t>{.size}</t>
